--- a/06_revision/validation/annotator_Akshat.xlsx
+++ b/06_revision/validation/annotator_Akshat.xlsx
@@ -983,8 +983,16 @@
           <t>hopefully bibi will come to his senses and stop this madness.</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>criticises netanyahu's conduct of the war</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
@@ -1008,8 +1016,16 @@
           <t>I don’t have it lol that’s why I’m hoping someone does…</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="n"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>asking for a video link, off topic chatter</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -1036,8 +1052,16 @@
 It’s all part of their plan</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="12" t="n"/>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>anti-palestine, accuses them of lying</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -1061,8 +1085,16 @@
           <t>Honestly you make a lot of assumptions in your own post, and your posting history suggests that you may be emotionally compromised. The ironic thing is that people will probably read the things you say and conclude that you express the very behaviors you are tired of from other people.</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="12" t="n"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>meta argument about user's post history, no clear stance</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -1085,8 +1117,16 @@
           <t>I dont agree with the creation of Israel. The British and American government caused this political problem and continue to deny there part. Im a White British male. Ive said this since the 1990s this conflict was inevitable. Why are humans so stubborn?</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="12" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>anti-zionist, disagrees with creation of israel</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1109,8 +1149,16 @@
           <t>​ @OscarB26  Damn straight!  Ana takes no prisoners and has zero tolerance for Genocide. She would crush Ben for all of us to see.</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="12" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>accuses israel of genocide, backs ana over ben</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -1133,8 +1181,16 @@
           <t>Lies. A-historical nonesense from a guy that needs to be ignored</t>
         </is>
       </c>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="12" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>fragment calling video lies, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
@@ -1158,8 +1214,16 @@
           <t>If you’re with some terrorists in a car it’s absolutely justified to kill you along with the terrorists.</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="12" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>defends idf strike on car with terrorists</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -1182,8 +1246,16 @@
           <t>Innocent civilians must never be harm. The roots causes of this atrocities must be resolved otherwise this will be a never ending conflict. The state of Israel should be forced to form a two state solution immediately 🙄 to the stop all this blood spilling</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="12" t="n"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>calls for forcing israel into 2ss to stop bloodshed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1206,8 +1278,16 @@
           <t xml:space="preserve"> @Mike-s9d  no one compared anything. Except you</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="12" t="n"/>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>reply arguing about comparisons, no stance</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -1230,8 +1310,16 @@
           <t>the amount of BS against Israel in the international press is appauling. You all drank the gaza koolaid.  Lets hope that israel can get the job done despite the information campaign against them.</t>
         </is>
       </c>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="12" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, defends idf against international press</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1254,8 +1342,16 @@
           <t>Many nations lost people and saw Palestinians dancing in the streets. Now they want our help against Israel. We will remain silent and hope Hamas does not use its women and children as shields.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>criticises palestinians and hamas, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="135" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -1280,8 +1376,16 @@
 In case of a second prisoner swap, Hamas has the order to give the most evil drugs to some of the remain hostages.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="12" t="n"/>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>anti-hamas, accuses hamas of drugging hostages</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="135" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1307,8 +1411,16 @@
 But let’s be honest. At this point, both of those setups are far off pipe dreams.</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="12" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>favours israeli sovereignty over palestinian areas</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1331,8 +1443,16 @@
           <t>Ejraelakhamanhoskasafayhnacahia</t>
         </is>
       </c>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="12" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>transliterated hindi wanting israel wiped out, anti-israel</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -1355,8 +1475,16 @@
           <t>Appo before 1917,who where in Jerusalem</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="12" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>question about jerusalem pre-1917, neutral inquiry</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -1379,8 +1507,16 @@
           <t>😢😢😢😢</t>
         </is>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="12" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>just crying emojis, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="120" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -1406,8 +1542,16 @@
 `The (Najran) delegation came to the Messenger of Allah in Al-Madinah, entered his Masjid wearing robes and garments, after the Prophet had prayed the `Asr prayer. They accompanied a caravan of camels led by Bani Al-Harith bin Ka`b. The Companions of the Messenger of Allah who saw them said that they never saw a delegation like them after that. When their worship time came, they stood up to perform their worship in the Prophet’s Masjid. Messenger of Allah said: “Let them (worship)” and they prayed towards east.</t>
         </is>
       </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="12" t="n"/>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>theological hadith discussion on praying in mosques, off topic</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -1431,8 +1575,16 @@
           <t>Yup :/ a large majority of us are struggling to get by paycheck to paycheck over here.</t>
         </is>
       </c>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="12" t="n"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>about living paycheck to paycheck in us, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -1457,8 +1609,16 @@
 If it were Israel's intention to wipe citizens in Gaza off the map it could have done so long ago, and there never would have been a need for a ground invasion risking the lives of Israeli soldiers.</t>
         </is>
       </c>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="12" t="n"/>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, defends iaf and denies genocide</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
@@ -1481,8 +1641,16 @@
           <t>At this point I'm convinced King Charles could run the country better than these delinquents.</t>
         </is>
       </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="12" t="n"/>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>uk domestic politics and king charles, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -1505,8 +1673,16 @@
           <t>What to expect from the people who choose barbavas over Jesus</t>
         </is>
       </c>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="12" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>antisemitic religious remark about barabbas, off topic</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -1530,8 +1706,16 @@
           <t>Being Queer and not closeted in Palestine they’d be 100% murdered in a horrific way as per Sharia law. Israel does not bomb them every year. And when they do, they give warning and instructions on where to go unlike any other army in the world. You can’t just make up statements and assume they’re fact. Right now is an anomaly, but a member of the Queer community in Palestine *STILL* has a better chance of survival than just coming out of the closet and living their true lives under Hamas.</t>
         </is>
       </c>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="12" t="n"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, contrasts idf warnings with sharia law under hamas</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -1555,8 +1739,16 @@
           <t>Watch them ignore or deny LMAO.</t>
         </is>
       </c>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="12" t="n"/>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>criticises israel for denying mosque bombings, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
@@ -1579,8 +1771,16 @@
           <t>Great history and also biblical time as well, the LA d of Israel belongs to the Jewish people ❤from Canada 🇨🇦</t>
         </is>
       </c>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="12" t="n"/>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, says land belongs to jewish people</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
@@ -1605,8 +1805,16 @@
 The point is that one of the best military trained nations in the world (if not the best in quality), it seems that cant defeat a single terrorist organization and for some reason killed, killing and will continue killing if nothing is changed mainly innocent children that has nothing to do with all this. This is called genocide.</t>
         </is>
       </c>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="12" t="n"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>accuses idf of genocide and killing children, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
@@ -1630,8 +1838,16 @@
           <t>70% of Palestinians in Gaza were either not born or too young to vote. And out of the obese who could vote, majority did NOT vote for Hamas. You have an absolute disgusting way of thinking</t>
         </is>
       </c>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="12" t="n"/>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>defends gazan civilians, rejects collective blame for hamas</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -1654,8 +1870,16 @@
           <t>💪💪💪🇮🇱🇮🇱</t>
         </is>
       </c>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="12" t="n"/>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>israeli flags and flex emojis, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
@@ -1679,8 +1903,16 @@
           <t>Turkey! Kind people without religious fanaticism</t>
         </is>
       </c>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="12" t="n"/>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>about favorite mena country being turkey, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="135" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -1712,8 +1944,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/Palestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="12" t="n"/>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>automod bot promoting unrwa and pro-palestine sub rules</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
@@ -1737,8 +1977,16 @@
           <t>inv link has expired..</t>
         </is>
       </c>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="12" t="n"/>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>broken invite link, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
@@ -1762,8 +2010,16 @@
           <t>Really the West Bank should be partitioned, with Jordan annexing areas A&amp;B and about half of area C, Israel annexing the remainder of area C, and residents in those areas being guaranteed full citizenship within 5 years so long as they accept Israeli/Jordanian sovereignty and renounce terrorist groups.</t>
         </is>
       </c>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="12" t="n"/>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>partition proposal involving jordan and israel, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
@@ -1786,8 +2042,16 @@
           <t>What's this nonsense ,ceasefire ceasefire yet BN says will attack rafah with or without CF,BN IS A warmonger</t>
         </is>
       </c>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="12" t="n"/>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>calls netanyahu a warmonger over rafah attack</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
@@ -1810,8 +2074,16 @@
           <t>Uh... Arabs are not the same blood as Israelis.</t>
         </is>
       </c>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="12" t="n"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>remark about blood and ethnicity, unclear stance</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -1834,8 +2106,16 @@
           <t>🕋🕋🫡🫡</t>
         </is>
       </c>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="12" t="n"/>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>kaaba and salute emojis, ambiguous stance on conflict</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
@@ -1859,8 +2139,16 @@
           <t>Because they aren't</t>
         </is>
       </c>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="12" t="n"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, denies israel is committing genocide</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
@@ -1884,8 +2172,16 @@
           <t>There are longer subway lines in the world. Could be an underground train</t>
         </is>
       </c>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="12" t="n"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>transit idea for connecting territories, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
@@ -1909,8 +2205,16 @@
           <t>Do you make it a habit of assuming minority groups are unable to reason beyond themselves, or do you save it just for the Jews?</t>
         </is>
       </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="12" t="n"/>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>defends jews against perceived bias, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
@@ -1934,8 +2238,16 @@
           <t>To be fair, that’s definitely a possibility, that is what hospitals are for after all.</t>
         </is>
       </c>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="12" t="n"/>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>defends hospital use for hostages, leans pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -1959,8 +2271,16 @@
           <t>Well you made a claim so you should back it up.</t>
         </is>
       </c>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="12" t="n"/>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>asks for proof of a claim, neutral debate comment</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
@@ -1987,8 +2307,16 @@
 amd the other points i mentioned earlier.</t>
         </is>
       </c>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="12" t="n"/>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>supports palestinian right of return and demands</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="90" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
@@ -2017,8 +2345,16 @@
 I guess it's a good thing you're not the arbiter of what is and isn't a democracy.</t>
         </is>
       </c>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="12" t="n"/>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>argues bedouins and druze aren't palestinian, pro-israel stance</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
@@ -2041,8 +2377,16 @@
           <t>❤❤❤</t>
         </is>
       </c>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="12" t="n"/>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>just heart emojis, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
@@ -2067,8 +2411,16 @@
 We are tired of your conflict, we are tired of you bringing your shit here.</t>
         </is>
       </c>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="12" t="n"/>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>european expressing fatigue with the conflict, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
@@ -2092,8 +2444,16 @@
           <t>Chad language, based af.</t>
         </is>
       </c>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="12" t="n"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>praising assyrian language, neutral remark</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
@@ -2116,8 +2476,16 @@
           <t>100% Truth, People Can’t Handle it.</t>
         </is>
       </c>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="12" t="n"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>generic agreement with video, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
@@ -2141,8 +2509,16 @@
           <t>Israel and the united states are like best bros. You can even see that when you enter a gift shop in Israel, you'll find things that are literally written "don't worry Israel, America stands with you" on them. It's a relationship based on mutual interests.</t>
         </is>
       </c>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="12" t="n"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>descriptive take on us-israel alliance, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="75" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
@@ -2168,8 +2544,16 @@
 You are no better than what you say the Palestinians are like. I thonk your worse.</t>
         </is>
       </c>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="12" t="n"/>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>criticises israel's weapons and us funding, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="8" t="inlineStr">
@@ -2193,8 +2577,16 @@
           <t>Thx</t>
         </is>
       </c>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="12" t="n"/>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>just 'thx', irrelevant noise</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
@@ -2217,8 +2609,16 @@
           <t>this is absolutely disgusting.</t>
         </is>
       </c>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="12" t="n"/>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>reaction without specifics, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="90" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
@@ -2243,8 +2643,16 @@
 That was textbook propaganda used by Joseph Goebbels against the Jewish people, as well as other enemies of the Nazi party. He was infamous for portraying the Jewish people as a wide variety of animals/monsters to dehumanize them and make people fear/hate them. One such example portrayed the Jewish people as lice and made accusations that they cause lice, and therefore should not live amongst “true aryans”.</t>
         </is>
       </c>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="12" t="n"/>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>compares israeli propaganda to nazi goebbels, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
@@ -2267,8 +2675,16 @@
           <t>Where is the report on Israeli tanks shooting on civiiian homes and helicopters firing at civilians ? Very limited report</t>
         </is>
       </c>
-      <c r="E56" s="11" t="n"/>
-      <c r="F56" s="12" t="n"/>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>demands coverage of idf firing on civilians, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
@@ -2291,8 +2707,16 @@
           <t>So sad</t>
         </is>
       </c>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="12" t="n"/>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>two words 'so sad', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
@@ -2315,8 +2739,16 @@
           <t>Exactly</t>
         </is>
       </c>
-      <c r="E58" s="11" t="n"/>
-      <c r="F58" s="12" t="n"/>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>single word 'exactly', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
@@ -2340,8 +2772,16 @@
           <t>I simply mean that Musk has never been fond of Jews or any other group that doesn’t conform to his idea of what should be normative.</t>
         </is>
       </c>
-      <c r="E59" s="11" t="n"/>
-      <c r="F59" s="12" t="n"/>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>comment on elon musk's attitudes, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
@@ -2365,8 +2805,16 @@
           <t>this is fucking horrible............ if those 2 dogs died other than that awesome video</t>
         </is>
       </c>
-      <c r="E60" s="11" t="n"/>
-      <c r="F60" s="12" t="n"/>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>cheers ambush on idf troops, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
@@ -2389,8 +2837,16 @@
           <t>Next time don't mess up with Israel</t>
         </is>
       </c>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="12" t="n"/>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel warning to enemies</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
@@ -2413,8 +2869,16 @@
           <t>The "P" word and the "G" word 😞</t>
         </is>
       </c>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="12" t="n"/>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>refers to palestine and genocide, leans pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
@@ -2437,8 +2901,16 @@
           <t>One word for him….INUTILE</t>
         </is>
       </c>
-      <c r="E63" s="11" t="n"/>
-      <c r="F63" s="12" t="n"/>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>insults speaker as useless, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
@@ -2462,8 +2934,16 @@
           <t>[removed]</t>
         </is>
       </c>
-      <c r="E64" s="11" t="n"/>
-      <c r="F64" s="12" t="n"/>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>removed comment, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
@@ -2488,8 +2968,16 @@
 Weird</t>
         </is>
       </c>
-      <c r="E65" s="11" t="n"/>
-      <c r="F65" s="12" t="n"/>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>accuses israel of funding hamas to destroy palestine</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
@@ -2513,8 +3001,16 @@
           <t>I'm sure it's easy to say things like that when you don't live in Israel (if this person actually does live in Israel, I apologize, but I'd be very confused)</t>
         </is>
       </c>
-      <c r="E66" s="11" t="n"/>
-      <c r="F66" s="12" t="n"/>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>defends israeli perspective against outside critics</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="8" t="inlineStr">
@@ -2537,8 +3033,16 @@
           <t>Billions</t>
         </is>
       </c>
-      <c r="E67" s="11" t="n"/>
-      <c r="F67" s="12" t="n"/>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>single word fragment, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="8" t="inlineStr">
@@ -2562,8 +3066,16 @@
           <t>As I'm getting older, I've come to realize that the so-called 'evils' are not always those we are told they are, such as Russia, Iran, Iraq, Syria, Libya, etc. Therefore, I'm 'anti-West,' but I also wish for peaceful negotiations and an end to bloodshed, especially in Ukraine. I support Russia and have always been a supporter of Palestine.</t>
         </is>
       </c>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="12" t="n"/>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>explicitly states support for palestine</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
@@ -2586,8 +3098,16 @@
           <t>Never forget 10/7!</t>
         </is>
       </c>
-      <c r="E69" s="11" t="n"/>
-      <c r="F69" s="12" t="n"/>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>remembers oct 7 attack, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
@@ -2611,8 +3131,16 @@
           <t>Asking for help to shoot down stuff violating your air space is completely compatible with not wanting other nations using your air space to attack people.</t>
         </is>
       </c>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="12" t="n"/>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>neutral explanation of jordan airspace defense</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="8" t="inlineStr">
@@ -2635,8 +3163,16 @@
           <t>Your explanation finally explained it  so that I could understand it.</t>
         </is>
       </c>
-      <c r="E71" s="11" t="n"/>
-      <c r="F71" s="12" t="n"/>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>compliment to video creator, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
@@ -2659,8 +3195,16 @@
           <t>Natanyahu</t>
         </is>
       </c>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="12" t="n"/>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>just netanyahu's name, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="8" t="inlineStr">
@@ -2683,8 +3227,16 @@
           <t>🇵🇸❤️🇵🇸❤️🇵🇸❤️🇵🇸</t>
         </is>
       </c>
-      <c r="E73" s="11" t="n"/>
-      <c r="F73" s="12" t="n"/>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>palestinian flags and hearts, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="90" customHeight="1">
       <c r="A74" s="8" t="inlineStr">
@@ -2713,8 +3265,16 @@
 Out of the roughly 200 water pipes(I think the number is accurate) given to Gaza, Hamas ripped them all out to create rocket launchers. Then you complain they are thirsty?</t>
         </is>
       </c>
-      <c r="E74" s="11" t="n"/>
-      <c r="F74" s="12" t="n"/>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>blames hamas for aid diversion and rockets, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
@@ -2738,8 +3298,16 @@
           <t>It's literally a news report with a narrator and writing below, its in Arabic</t>
         </is>
       </c>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="12" t="n"/>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>describing format of video, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="45" customHeight="1">
       <c r="A76" s="8" t="inlineStr">
@@ -2764,8 +3332,16 @@
           <t>Oh c'mon it's clear by the way he posted this and the title</t>
         </is>
       </c>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="12" t="n"/>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>meta comment on russia-ukraine post, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
@@ -2789,8 +3365,16 @@
 Terrorist ppl too..</t>
         </is>
       </c>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="12" t="n"/>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>anti-palestinian rhetoric mocking peaceful claim, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="90" customHeight="1">
       <c r="A78" s="8" t="inlineStr">
@@ -2814,8 +3398,16 @@
           <t>lmao this is the same as when people like him call for the defunding or complete removal of law enforcement and police departments around the nation. The end result higher crime rate, soft of crime prosecutors and degradation of public safety. Yep, this is sadly why so many center left and liberals are no longer interested in supporting the Democrat party. We'll see what happens in the upcoming election but i wouldn't be surprised if Biden loses to Trump without considering these factors</t>
         </is>
       </c>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="12" t="n"/>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>rant about us politics and police defunding, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="8" t="inlineStr">
@@ -2838,8 +3430,16 @@
           <t>I just need to point out these where probably not Hamas fighters they where more likely qasam brigade fighters</t>
         </is>
       </c>
-      <c r="E79" s="11" t="n"/>
-      <c r="F79" s="12" t="n"/>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>pedantic factual distinction on brigades, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="8" t="inlineStr">
@@ -2863,8 +3463,16 @@
           <t>Your dad</t>
         </is>
       </c>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="12" t="n"/>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>childish insult, irrelevant spam</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="75" customHeight="1">
       <c r="A81" s="8" t="inlineStr">
@@ -2888,8 +3496,16 @@
           <t>Thank you!  This is a horrible situation all around and I could understand some people not getting it and thinking we should ceasefire ( we should not) , but the hate and vitriol, justifying and denying the atrocities, chanting from the river to the sea, making Jews all over the world feel unsafe, it's so far over the top and I'm glad I'm in Israel now, even though it's a bit scary here, and not in the US trying to navigate this.</t>
         </is>
       </c>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="12" t="n"/>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>opposes ceasefire, expresses solidarity with israel</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="8" t="inlineStr">
@@ -2913,8 +3529,16 @@
           <t>Can you quote the relevant section?</t>
         </is>
       </c>
-      <c r="E82" s="11" t="n"/>
-      <c r="F82" s="12" t="n"/>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>neutral request for citation</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="45" customHeight="1">
       <c r="A83" s="8" t="inlineStr">
@@ -2937,8 +3561,16 @@
           <t>Mi corazón al pueblo de Israel , nosotros creemos en Yeshua/Jesus al mismo tiempo creemos que el tanaj (antiguo testamento) sigue vigente, y también leemos la Torah así como al Rabino dijo es exactamente como nosotros lo entendemos, estamos en el mismo entendimiento.</t>
         </is>
       </c>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="12" t="n"/>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>christian support for the people of israel, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="60" customHeight="1">
       <c r="A84" s="8" t="inlineStr">
@@ -2962,8 +3594,16 @@
           <t>https://apnews.com/article/israel-hamas-war-gaza-health-ministry-health-death-toll-59470820308b31f1faf73c703400b033 look at how close the previous death stats are between Gaza and official UN totals for previous wars. I personally think Hamas is full of crap, but the health ministry has been the only reliable part of Gaza’s government for a while.</t>
         </is>
       </c>
-      <c r="E84" s="11" t="n"/>
-      <c r="F84" s="12" t="n"/>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>defends gaza health ministry death toll, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="8" t="inlineStr">
@@ -2986,8 +3626,16 @@
           <t>I want my tax money back. The UK population stands with Palestinians.</t>
         </is>
       </c>
-      <c r="E85" s="11" t="n"/>
-      <c r="F85" s="12" t="n"/>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>demands tax refund, stands with palestinians</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
@@ -3011,8 +3659,16 @@
           <t>It literally shows in the first study that Ashkenazis are more closely related to Levantine or other middle eastern people than Europeans.</t>
         </is>
       </c>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="12" t="n"/>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>argues jewish levantine roots via genetics, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
@@ -3035,8 +3691,16 @@
           <t>This interview was very informing. Thank you for bringing Dr Gabor. He's a wise soul who has high moral</t>
         </is>
       </c>
-      <c r="E87" s="11" t="n"/>
-      <c r="F87" s="12" t="n"/>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>praises gabor mate's pro-palestinian critique</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
@@ -3060,8 +3724,16 @@
           <t>Are you 12 years old? Please be at least 25 before continuing this thread.</t>
         </is>
       </c>
-      <c r="E88" s="11" t="n"/>
-      <c r="F88" s="12" t="n"/>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr">
+        <is>
+          <t>insulting user's age, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="8" t="inlineStr">
@@ -3084,8 +3756,16 @@
           <t>We love israel❤</t>
         </is>
       </c>
-      <c r="E89" s="11" t="n"/>
-      <c r="F89" s="12" t="n"/>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel love message</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="8" t="inlineStr">
@@ -3109,8 +3789,16 @@
           <t>Also, are you not aware of them demolishing religious buildings in countries like pakistan, Ismaeli mosques and churches being blown up in broad daylight</t>
         </is>
       </c>
-      <c r="E90" s="11" t="n"/>
-      <c r="F90" s="12" t="n"/>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>about sectarian violence in pakistan, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="8" t="inlineStr">
@@ -3134,8 +3822,16 @@
           <t>Hey man free speech only works if you listen to things you don't agree with and accept that person's right to say it. I believe all humans have the capacity for good. I wish you all the best</t>
         </is>
       </c>
-      <c r="E91" s="11" t="n"/>
-      <c r="F91" s="12" t="n"/>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>general comment on free speech and tolerance, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
@@ -3159,8 +3855,16 @@
           <t>His constituents like it</t>
         </is>
       </c>
-      <c r="E92" s="11" t="n"/>
-      <c r="F92" s="12" t="n"/>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>factual comment on fetterman's voters, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="8" t="inlineStr">
@@ -3183,8 +3887,16 @@
           <t>7'Okt 23 NEVER FORGET  🙏😢❤🇮🇱</t>
         </is>
       </c>
-      <c r="E93" s="11" t="n"/>
-      <c r="F93" s="12" t="n"/>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>mourns oct 7 with israeli flag, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="8" t="inlineStr">
@@ -3208,8 +3920,16 @@
           <t>Bless your heart, you seem like a very kind soul. Your husband is lucky to have you</t>
         </is>
       </c>
-      <c r="E94" s="11" t="n"/>
-      <c r="F94" s="12" t="n"/>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>friendly personal compliment, off-topic</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="8" t="inlineStr">
@@ -3232,8 +3952,16 @@
           <t xml:space="preserve"> @silkroadcaravan  'From the River to the Sea' is also a slogan used by Zionists.</t>
         </is>
       </c>
-      <c r="E95" s="11" t="n"/>
-      <c r="F95" s="12" t="n"/>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr">
+        <is>
+          <t>counters river-to-sea criticism by citing zionist use, leans p</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="45" customHeight="1">
       <c r="A96" s="8" t="inlineStr">
@@ -3256,8 +3984,16 @@
           <t xml:space="preserve"> @BillAnt  he was  using dark humor at times but he wasn’t  trying to be funny. It went viral and everyone was amazed how he presented his position. Do you know that piers went for the second round?</t>
         </is>
       </c>
-      <c r="E96" s="11" t="n"/>
-      <c r="F96" s="12" t="n"/>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>praises bassem youssef's viral pro-palestine interview</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="8" t="inlineStr">
@@ -3281,8 +4017,16 @@
 I like it</t>
         </is>
       </c>
-      <c r="E97" s="11" t="n"/>
-      <c r="F97" s="12" t="n"/>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr">
+        <is>
+          <t>generic comment on humor, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="8" t="inlineStr">
@@ -3305,8 +4049,16 @@
           <t>Fox has been reporting on this from day 1.</t>
         </is>
       </c>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="12" t="n"/>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>mentioning fox news coverage, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="8" t="inlineStr">
@@ -3329,8 +4081,16 @@
           <t>They never should of attacked Israel this is what happens</t>
         </is>
       </c>
-      <c r="E99" s="11" t="n"/>
-      <c r="F99" s="12" t="n"/>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>blames attack on israel for destruction, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="60" customHeight="1">
       <c r="A100" s="8" t="inlineStr">
@@ -3353,8 +4113,16 @@
           <t xml:space="preserve"> @Twiddlers  the name really doesn't matter. The issue is with the recreation of a state just because it existed almost 2000 years after it fell for people who haven't been in the land for almost 2000 years. Would you also recreate the Aztec, Al-Andalus, the Mayan state or one of the many thousands of kingdoms that have risen and fallen or is this unique to God's chosen people?</t>
         </is>
       </c>
-      <c r="E100" s="11" t="n"/>
-      <c r="F100" s="12" t="n"/>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>anti-zionist, questions historic right to statehood</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="8" t="inlineStr">
@@ -3378,8 +4146,16 @@
           <t>Exactly. Or their "famine".</t>
         </is>
       </c>
-      <c r="E101" s="11" t="n"/>
-      <c r="F101" s="12" t="n"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
+        <is>
+          <t>denies genocide and dismisses famine, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="75" customHeight="1">
       <c r="A102" s="8" t="inlineStr">
@@ -3406,8 +4182,16 @@
 https://english.alarabiya.net/amp/perspective/analysis/2015/08/17/RE-EXPOSED-A-horrific-story-of-Israeli-rape-and-murder-in-1949</t>
         </is>
       </c>
-      <c r="E102" s="11" t="n"/>
-      <c r="F102" s="12" t="n"/>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>cites reports of idf sexual violence against palestinians</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="8" t="inlineStr">
@@ -3431,8 +4215,16 @@
           <t>And only in such situation will Hezbollah attack Israel, as will Iran. It will rain missiles in Israel.</t>
         </is>
       </c>
-      <c r="E103" s="11" t="n"/>
-      <c r="F103" s="12" t="n"/>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>predicts missiles raining on israel, anti-israel tone</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="8" t="inlineStr">
@@ -3455,8 +4247,16 @@
           <t>Proof, cite your sources. Not just the stuff the IDF says, actual 3rd party sources</t>
         </is>
       </c>
-      <c r="E104" s="11" t="n"/>
-      <c r="F104" s="12" t="n"/>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>rejects idf claims, demands 3rd party proof</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="8" t="inlineStr">
@@ -3479,8 +4279,16 @@
           <t>How can make this my ringing tune pls?</t>
         </is>
       </c>
-      <c r="E105" s="11" t="n"/>
-      <c r="F105" s="12" t="n"/>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr">
+        <is>
+          <t>asking for a ringtone, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
@@ -3503,8 +4311,16 @@
           <t>Just like the Germans did. History repeats in strange ways</t>
         </is>
       </c>
-      <c r="E106" s="11" t="n"/>
-      <c r="F106" s="12" t="n"/>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>compares israeli actions to nazi germany, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="45" customHeight="1">
       <c r="A107" s="8" t="inlineStr">
@@ -3528,8 +4344,16 @@
           <t>When you get a chance, please forward me some of your sources. I haven’t slept much in the last month and feel like i read everything I could to educate myself. Would love to see your perspective backed by the history books you mentioned. Sway my opinion</t>
         </is>
       </c>
-      <c r="E107" s="11" t="n"/>
-      <c r="F107" s="12" t="n"/>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>polite request for history book recommendations, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="135" customHeight="1">
       <c r="A108" s="8" t="inlineStr">
@@ -3557,8 +4381,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/IsraelPalestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E108" s="11" t="n"/>
-      <c r="F108" s="12" t="n"/>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>subreddit bot warning on nazi rules, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="8" t="inlineStr">
@@ -3581,8 +4413,16 @@
           <t>Free Palestine 😢</t>
         </is>
       </c>
-      <c r="E109" s="11" t="n"/>
-      <c r="F109" s="12" t="n"/>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>free palestine slogan, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="8" t="inlineStr">
@@ -3605,8 +4445,16 @@
           <t>AstagfirAllah</t>
         </is>
       </c>
-      <c r="E110" s="11" t="n"/>
-      <c r="F110" s="12" t="n"/>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>arabic religious exclamation of distress, unclear stance</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="8" t="inlineStr">
@@ -3629,8 +4477,16 @@
           <t>Yes, agreed.</t>
         </is>
       </c>
-      <c r="E111" s="11" t="n"/>
-      <c r="F111" s="12" t="n"/>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>generic agreement, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="45" customHeight="1">
       <c r="A112" s="8" t="inlineStr">
@@ -3654,8 +4510,16 @@
           <t>UN first aid kits are not meant to be used by the military. They are sent into Gaza for civilian use. The fact that Hamas has them either means they are stealing international aid for themselves or the UN is illegally giving it to them.</t>
         </is>
       </c>
-      <c r="E112" s="11" t="n"/>
-      <c r="F112" s="12" t="n"/>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>accuses hamas of stealing un aid, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="8" t="inlineStr">
@@ -3679,8 +4543,16 @@
           <t>Why mention the red army veterans? What is the link to israei army?</t>
         </is>
       </c>
-      <c r="E113" s="11" t="n"/>
-      <c r="F113" s="12" t="n"/>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>clarifying question about post text, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="120" customHeight="1">
       <c r="A114" s="8" t="inlineStr">
@@ -3707,8 +4579,16 @@
 + Compile a list of Canadian companies, small and large, that Canadians can support - post it here and also make a simple one page website that lists them - the more information about who we can support (and non supporters) would be a great way to volunteer time to help at home.</t>
         </is>
       </c>
-      <c r="E114" s="11" t="n"/>
-      <c r="F114" s="12" t="n"/>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>action plan to promote palestinian books and bds</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="75" customHeight="1">
       <c r="A115" s="8" t="inlineStr">
@@ -3731,8 +4611,16 @@
           <t>psychological analysis of her facial expressions at key points of the diatribe indicate that she experienced a degree of satisfaction from the October 7th attacks.  As she accessed the imagery of the attack in her head, at the moment he was referencing it, the slight grin and tongue thrust indicate pleasure or satisfaction.  She has deep seated resentment and hate for Israel.  Which is not  surprising given the atrocities that have been perpetrated by both sides.</t>
         </is>
       </c>
-      <c r="E115" s="11" t="n"/>
-      <c r="F115" s="12" t="n"/>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>facial analysis, notes atrocities by both sides, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="8" t="inlineStr">
@@ -3755,8 +4643,16 @@
           <t>This ambassador palestinian big liar</t>
         </is>
       </c>
-      <c r="E116" s="11" t="n"/>
-      <c r="F116" s="12" t="n"/>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>calls palestinian ambassador a liar, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="8" t="inlineStr">
@@ -3779,8 +4675,16 @@
           <t>Whatever the reason .. I must support humanity ... Think about your children if they suffer like gaza children. ..</t>
         </is>
       </c>
-      <c r="E117" s="11" t="n"/>
-      <c r="F117" s="12" t="n"/>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>plea for gaza children suffering, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="8" t="inlineStr">
@@ -3803,8 +4707,16 @@
           <t xml:space="preserve"> @ShadowBro6992  As a HUMAN dawg... Not as a TERRORIST</t>
         </is>
       </c>
-      <c r="E118" s="11" t="n"/>
-      <c r="F118" s="12" t="n"/>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>interpersonal exchange about humanity vs terrorist, unclear stance</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="8" t="inlineStr">
@@ -3827,8 +4739,16 @@
           <t>11:40 dont bring a gun to a missil fight</t>
         </is>
       </c>
-      <c r="E119" s="11" t="n"/>
-      <c r="F119" s="12" t="n"/>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>quip on missile vs gun firepower, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="8" t="inlineStr">
@@ -3852,8 +4772,16 @@
           <t>Read what? The international condemnations or the excuses that the idf ises when kidnapping children?</t>
         </is>
       </c>
-      <c r="E120" s="11" t="n"/>
-      <c r="F120" s="12" t="n"/>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>accuses idf of kidnapping children, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="8" t="inlineStr">
@@ -3877,8 +4805,16 @@
           <t>Oh i remember this one! They claimed we hired Ukrainians soldiers to fight for us, cause the IDF is "too weak" lol</t>
         </is>
       </c>
-      <c r="E121" s="11" t="n"/>
-      <c r="F121" s="12" t="n"/>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel user mocks anti-idf rumors</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="8" t="inlineStr">
@@ -3901,8 +4837,16 @@
           <t>And nothing else. Si disarmed</t>
         </is>
       </c>
-      <c r="E122" s="11" t="n"/>
-      <c r="F122" s="12" t="n"/>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>fragment comment, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
@@ -3925,8 +4869,16 @@
           <t>Oh it has. People just turn away and say it’s fake. Or that they forced them to say things</t>
         </is>
       </c>
-      <c r="E123" s="11" t="n"/>
-      <c r="F123" s="12" t="n"/>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>ambiguous remark about claims being fake, unclear stance</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="8" t="inlineStr">
@@ -3949,8 +4901,16 @@
           <t>I will never forgive or forget what is happening to Palestinian people 😢</t>
         </is>
       </c>
-      <c r="E124" s="11" t="n"/>
-      <c r="F124" s="12" t="n"/>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>stands with palestinians against suffering, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="8" t="inlineStr">
@@ -3974,8 +4934,16 @@
           <t>Legit the best present. 🎁</t>
         </is>
       </c>
-      <c r="E125" s="11" t="n"/>
-      <c r="F125" s="12" t="n"/>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>supportive reaction on pro-israel thread</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
@@ -3998,8 +4966,16 @@
           <t>No bruh he isnt too smart as he acts like no one killed babies besides the idf bruh😂</t>
         </is>
       </c>
-      <c r="E126" s="11" t="n"/>
-      <c r="F126" s="12" t="n"/>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>criticises sole focus on idf baby killings, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
@@ -4023,8 +4999,16 @@
           <t>Sure.</t>
         </is>
       </c>
-      <c r="E127" s="11" t="n"/>
-      <c r="F127" s="12" t="n"/>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>one-word reply 'sure', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="8" t="inlineStr">
@@ -4048,8 +5032,16 @@
           <t>Do you know the meaning of the word Zion?</t>
         </is>
       </c>
-      <c r="E128" s="11" t="n"/>
-      <c r="F128" s="12" t="n"/>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>socratic question about meaning of zion, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="8" t="inlineStr">
@@ -4072,8 +5064,16 @@
           <t>Aap kisko support karte ho</t>
         </is>
       </c>
-      <c r="E129" s="11" t="n"/>
-      <c r="F129" s="12" t="n"/>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>hindi question asking who creator supports, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="8" t="inlineStr">
@@ -4096,8 +5096,16 @@
           <t>God bless South Afrika and its RUGBY!</t>
         </is>
       </c>
-      <c r="E130" s="11" t="n"/>
-      <c r="F130" s="12" t="n"/>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>cheering south african rugby, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="8" t="inlineStr">
@@ -4121,8 +5129,16 @@
           <t>If you are right then that is a great sign for the future and something I didn't know about. Thank you.</t>
         </is>
       </c>
-      <c r="E131" s="11" t="n"/>
-      <c r="F131" s="12" t="n"/>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="inlineStr">
+        <is>
+          <t>courteous dialogue with palestinian user, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="135" customHeight="1">
       <c r="A132" s="8" t="inlineStr">
@@ -4154,8 +5170,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/Palestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E132" s="11" t="n"/>
-      <c r="F132" s="12" t="n"/>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>automod bot promoting unrwa and rules</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="75" customHeight="1">
       <c r="A133" s="8" t="inlineStr">
@@ -4180,8 +5204,16 @@
 while i agree with your take for the most part, aren't these people to blame for their poor decisions- they made the decision to live on someone else's land and tie their livelihood to it.</t>
         </is>
       </c>
-      <c r="E133" s="11" t="n"/>
-      <c r="F133" s="12" t="n"/>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>blames displaced palestinian tenant farmers, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="60" customHeight="1">
       <c r="A134" s="8" t="inlineStr">
@@ -4205,8 +5237,16 @@
           <t>I can’t take the credit, the Palestinians showed me unbelievable strength, only possible from a higher power. I picked up the Quran and started reading it for the first time after being admittedly agnostic for a while. I have to say it’s making too much sense to be denied! Ashhadu ala ilaha illallah.</t>
         </is>
       </c>
-      <c r="E134" s="11" t="n"/>
-      <c r="F134" s="12" t="n"/>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>inspired by palestinian strength to embrace islam</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="8" t="inlineStr">
@@ -4230,8 +5270,16 @@
           <t>The same can be said about the rich Zionist organizations.</t>
         </is>
       </c>
-      <c r="E135" s="11" t="n"/>
-      <c r="F135" s="12" t="n"/>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>criticises rich zionist orgs, leans pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
@@ -4255,8 +5303,16 @@
           <t>Only innocent ones are the babies and young children. F everyone else in gaza</t>
         </is>
       </c>
-      <c r="E136" s="11" t="n"/>
-      <c r="F136" s="12" t="n"/>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>hostile toward adult gazans, pro-israel anger</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="8" t="inlineStr">
@@ -4280,8 +5336,16 @@
           <t>I don't think anyone will prompt an attack on Lebanon or Iran without a very good reason.</t>
         </is>
       </c>
-      <c r="E137" s="11" t="n"/>
-      <c r="F137" s="12" t="n"/>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>speculation on lebanon/iran escalation, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="8" t="inlineStr">
@@ -4304,8 +5368,16 @@
           <t>Allah o Akbar❤</t>
         </is>
       </c>
-      <c r="E138" s="11" t="n"/>
-      <c r="F138" s="12" t="n"/>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>religious takbir with heart, ambiguous stance</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
@@ -4328,8 +5400,16 @@
           <t xml:space="preserve"> @truthadvocate786 he is a virgin but not part of the 72 😂</t>
         </is>
       </c>
-      <c r="E139" s="11" t="n"/>
-      <c r="F139" s="12" t="n"/>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>vulgar joke about 72 virgins, irrelevant banter</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="8" t="inlineStr">
@@ -4353,8 +5433,16 @@
           <t>You will instead get invited to be interviewed on live television</t>
         </is>
       </c>
-      <c r="E140" s="11" t="n"/>
-      <c r="F140" s="12" t="n"/>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>cynical remark on pro-israel media platforming</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="8" t="inlineStr">
@@ -4378,8 +5466,16 @@
 Both Countries Should be Accepted Two nation theroy...🙏</t>
         </is>
       </c>
-      <c r="E141" s="11" t="n"/>
-      <c r="F141" s="12" t="n"/>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>calls for two-state solution and humanity, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="8" t="inlineStr">
@@ -4402,8 +5498,16 @@
           <t>If those were Hamas soldiers they would have called this a terrorist attack. This is insane.</t>
         </is>
       </c>
-      <c r="E142" s="11" t="n"/>
-      <c r="F142" s="12" t="n"/>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>calls out western hypocrisy on terrorism, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="8" t="inlineStr">
@@ -4426,8 +5530,16 @@
           <t>Free Palestine 🇵🇸</t>
         </is>
       </c>
-      <c r="E143" s="11" t="n"/>
-      <c r="F143" s="12" t="n"/>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="inlineStr">
+        <is>
+          <t>free palestine slogan and flag</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="8" t="inlineStr">
@@ -4451,8 +5563,16 @@
           <t>I think Netanyahu should follow what the ICJ said and show the world that Israel is NOT committing genocide</t>
         </is>
       </c>
-      <c r="E144" s="11" t="n"/>
-      <c r="F144" s="12" t="n"/>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>wants israel to follow icj to prove no genocide</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
@@ -4475,8 +5595,16 @@
           <t>What now? Un officials from these countries should be ashamed of themselves. Hospital being bombed. Shame on you</t>
         </is>
       </c>
-      <c r="E145" s="11" t="n"/>
-      <c r="F145" s="12" t="n"/>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>condemns hospital bombing and un inaction, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="8" t="inlineStr">
@@ -4499,8 +5627,16 @@
           <t>Uk is complicit</t>
         </is>
       </c>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="12" t="n"/>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>accuses uk of complicity with israel, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="45" customHeight="1">
       <c r="A147" s="8" t="inlineStr">
@@ -4523,8 +5659,16 @@
           <t>​ @victoriabond7739 that's what Israel want already they want people in gaza leave to occupy palastine permanently but our brothers and sisters don't want to give up and god chose palastine to suffer all this because they didn't give up and they will never</t>
         </is>
       </c>
-      <c r="E147" s="11" t="n"/>
-      <c r="F147" s="12" t="n"/>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F147" s="12" t="inlineStr">
+        <is>
+          <t>accuses israel of permanent occupation, backs palestinians</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="45" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
@@ -4548,8 +5692,16 @@
           <t>Exactly as I thought a disingenuous response from an extremist. You know what’s worse is people like you will call for war, genocide, extermination while you sit in your cosy comfortable house on Reddit. Playing the whatabout game is literally no benefit for anyone</t>
         </is>
       </c>
-      <c r="E148" s="11" t="n"/>
-      <c r="F148" s="12" t="n"/>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>accuses pro-war commenter of supporting genocide</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="8" t="inlineStr">
@@ -4572,8 +5724,16 @@
           <t>A normal Human being !!</t>
         </is>
       </c>
-      <c r="E149" s="11" t="n"/>
-      <c r="F149" s="12" t="n"/>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F149" s="12" t="inlineStr">
+        <is>
+          <t>generic compliment to speaker, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="8" t="inlineStr">
@@ -4597,8 +5757,16 @@
           <t>Thousands. When you're unemployed and have spent your life saving and planning for something, it just hurts. I know I'm a bit selfish right now but it's something I have to think about.</t>
         </is>
       </c>
-      <c r="E150" s="11" t="n"/>
-      <c r="F150" s="12" t="n"/>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F150" s="12" t="inlineStr">
+        <is>
+          <t>personal financial worry during rocket fire, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="8" t="inlineStr">
@@ -4621,8 +5789,16 @@
           <t>Just amazing and astonishing.</t>
         </is>
       </c>
-      <c r="E151" s="11" t="n"/>
-      <c r="F151" s="12" t="n"/>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F151" s="12" t="inlineStr">
+        <is>
+          <t>generic praise, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="8" t="inlineStr">
@@ -4645,8 +5821,16 @@
           <t>So he support Israel-zionist attack the unarmed muslim while they pray in the mosque during Ramadhan? Thats more unacceptable ever in any situations.</t>
         </is>
       </c>
-      <c r="E152" s="11" t="n"/>
-      <c r="F152" s="12" t="n"/>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>condemns israeli attacks on al-aqsa worshippers</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="60" customHeight="1">
       <c r="A153" s="8" t="inlineStr">
@@ -4670,8 +5854,16 @@
           <t>...or in the Balkans. The Ottoman empire made a lot of enemies, very few people in the area they didn't invade, massacre or enslave. However relations between Persia and the Ottoman's was *relatively* very peaceful. I agree with plenty of people here, if anyone likes the Turks it's probably Iranians.</t>
         </is>
       </c>
-      <c r="E153" s="11" t="n"/>
-      <c r="F153" s="12" t="n"/>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F153" s="12" t="inlineStr">
+        <is>
+          <t>about persian and ottoman history, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
@@ -4695,8 +5887,16 @@
           <t>I love their enthusiasm</t>
         </is>
       </c>
-      <c r="E154" s="11" t="n"/>
-      <c r="F154" s="12" t="n"/>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>cheers anti-israel sentiment on weibo, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="45" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
@@ -4720,8 +5920,16 @@
           <t>Most of what you wrote was baseless nonsense but regarding the helicopter and the Haaretz report - the helicopter arrived at the festival area about 5 hours after the massacre started so your/Al-Jazeera's argument is ridiculous.</t>
         </is>
       </c>
-      <c r="E155" s="11" t="n"/>
-      <c r="F155" s="12" t="n"/>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>debunks idf friendly-fire claims at nova, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="8" t="inlineStr">
@@ -4745,8 +5953,16 @@
 He is doing nothing but lip service</t>
         </is>
       </c>
-      <c r="E156" s="11" t="n"/>
-      <c r="F156" s="12" t="n"/>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F156" s="12" t="inlineStr">
+        <is>
+          <t>criticises rishi sunak's handling of gaza crisis</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
@@ -4769,8 +5985,16 @@
           <t>Fake</t>
         </is>
       </c>
-      <c r="E157" s="11" t="n"/>
-      <c r="F157" s="12" t="n"/>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F157" s="12" t="inlineStr">
+        <is>
+          <t>single word 'fake', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="45" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
@@ -4793,8 +6017,16 @@
           <t>An eye for an eye a tooth for a tooth when will these people stop murdering each other stop killing in the name of ur god.stop hating each other.we are all stuck on this planet so learn to get along.think of john lennons song imagine.</t>
         </is>
       </c>
-      <c r="E158" s="11" t="n"/>
-      <c r="F158" s="12" t="n"/>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>pacifist plea against both sides killing, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="135" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
@@ -4826,8 +6058,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/Palestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E159" s="11" t="n"/>
-      <c r="F159" s="12" t="n"/>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>automod bot promoting unrwa and rules</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
@@ -4850,8 +6090,16 @@
           <t>This reporter is walking through this killing field wearing slippers ???</t>
         </is>
       </c>
-      <c r="E160" s="11" t="n"/>
-      <c r="F160" s="12" t="n"/>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F160" s="12" t="inlineStr">
+        <is>
+          <t>noticing reporter in slippers, neutral observation</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
@@ -4874,8 +6122,16 @@
           <t>Extremely informative. Thank you for the clarity.</t>
         </is>
       </c>
-      <c r="E161" s="11" t="n"/>
-      <c r="F161" s="12" t="n"/>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>thanking creator for informative video, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="60" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
@@ -4900,8 +6156,16 @@
 It’s like if I crept into the house of some poor guy a few neighborhoods away, and told him that I now owned 51% of his house.</t>
         </is>
       </c>
-      <c r="E162" s="11" t="n"/>
-      <c r="F162" s="12" t="n"/>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F162" s="12" t="inlineStr">
+        <is>
+          <t>compares israel's creation to home theft, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="8" t="inlineStr">
@@ -4924,8 +6188,16 @@
           <t>InsyaAllah - NO!</t>
         </is>
       </c>
-      <c r="E163" s="11" t="n"/>
-      <c r="F163" s="12" t="n"/>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>short exclamation, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="45" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
@@ -4949,8 +6221,16 @@
           <t>This is amazingly comical how you are trying to defend this when the very simple fact that is the IOF is surrounding the church and they have snipers and the two women killed were by sniper fire. Otherwise how would they be targeted ?</t>
         </is>
       </c>
-      <c r="E164" s="11" t="n"/>
-      <c r="F164" s="12" t="n"/>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F164" s="12" t="inlineStr">
+        <is>
+          <t>condemns idf snipers killing women in church, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
@@ -4974,8 +6254,16 @@
           <t>The occupation only began in 1967</t>
         </is>
       </c>
-      <c r="E165" s="11" t="n"/>
-      <c r="F165" s="12" t="n"/>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>argues occupation only dates to 1967, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
@@ -4999,8 +6287,16 @@
           <t>Tbh this is not the first time they do this, its been happening again and again and again, there is no way this is going to end well for anyone</t>
         </is>
       </c>
-      <c r="E166" s="11" t="n"/>
-      <c r="F166" s="12" t="n"/>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F166" s="12" t="inlineStr">
+        <is>
+          <t>fatalistic take on recurring violence, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="8" t="inlineStr">
@@ -5023,8 +6319,16 @@
           <t>It's not aid, it's weapons.  Where else is Hamas getting all of these rockets from?</t>
         </is>
       </c>
-      <c r="E167" s="11" t="n"/>
-      <c r="F167" s="12" t="n"/>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F167" s="12" t="inlineStr">
+        <is>
+          <t>claims gaza aid is actually weapons, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="75" customHeight="1">
       <c r="A168" s="8" t="inlineStr">
@@ -5048,8 +6352,16 @@
 Therefore, I advise western politicians to lift their dirty hands and lift Israel along with them and leave Palestine to their own and learn from them the meaning of cosmopolitan.</t>
         </is>
       </c>
-      <c r="E168" s="11" t="n"/>
-      <c r="F168" s="12" t="n"/>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>calls for removing western support for israel, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="8" t="inlineStr">
@@ -5072,8 +6384,16 @@
           <t>Me and many others</t>
         </is>
       </c>
-      <c r="E169" s="11" t="n"/>
-      <c r="F169" s="12" t="n"/>
+      <c r="E169" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F169" s="12" t="inlineStr">
+        <is>
+          <t>fragment 'me and many others', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="8" t="inlineStr">
@@ -5096,8 +6416,16 @@
           <t>Antisemitic ten years ago? Hill, you’ve been engaging in antisemitic hate all day today.</t>
         </is>
       </c>
-      <c r="E170" s="11" t="n"/>
-      <c r="F170" s="12" t="n"/>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>accuses marc lamont hill of antisemitism, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="8" t="inlineStr">
@@ -5120,8 +6448,16 @@
           <t>the fact he shares his food first for the joy of others is very touching!</t>
         </is>
       </c>
-      <c r="E171" s="11" t="n"/>
-      <c r="F171" s="12" t="n"/>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F171" s="12" t="inlineStr">
+        <is>
+          <t>touching comment on food sharing, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="75" customHeight="1">
       <c r="A172" s="8" t="inlineStr">
@@ -5145,8 +6481,16 @@
           <t>I mean, so long as you openly and happily say “Israel has a right to exist with its current borders, and any attempts to bring about its downfall are invalid and unjustified”, this is really more for your sake than mine. I’m just trying to let you know that there’s a hole in your understanding. It appears that when you hear “the occupation of Palestine”, what you think is being said is not what is in fact being said.</t>
         </is>
       </c>
-      <c r="E172" s="11" t="n"/>
-      <c r="F172" s="12" t="n"/>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F172" s="12" t="inlineStr">
+        <is>
+          <t>challenges pro-israel narrative on borders and occupation</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="8" t="inlineStr">
@@ -5169,8 +6513,16 @@
           <t>Emoji 😂.</t>
         </is>
       </c>
-      <c r="E173" s="11" t="n"/>
-      <c r="F173" s="12" t="n"/>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F173" s="12" t="inlineStr">
+        <is>
+          <t>meta comment on emoji, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="8" t="inlineStr">
@@ -5194,8 +6546,16 @@
           <t>Yeah, I'm not going to listen to a podcast of a random someone.</t>
         </is>
       </c>
-      <c r="E174" s="11" t="n"/>
-      <c r="F174" s="12" t="n"/>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F174" s="12" t="inlineStr">
+        <is>
+          <t>refusing to listen to podcast, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="8" t="inlineStr">
@@ -5218,8 +6578,16 @@
           <t>Delusional JOE</t>
         </is>
       </c>
-      <c r="E175" s="11" t="n"/>
-      <c r="F175" s="12" t="n"/>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F175" s="12" t="inlineStr">
+        <is>
+          <t>insults joe biden, unclear stance on conflict</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="8" t="inlineStr">
@@ -5242,8 +6610,16 @@
           <t>That's Palestinian land</t>
         </is>
       </c>
-      <c r="E176" s="11" t="n"/>
-      <c r="F176" s="12" t="n"/>
+      <c r="E176" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F176" s="12" t="inlineStr">
+        <is>
+          <t>asserts land is palestinian, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="45" customHeight="1">
       <c r="A177" s="8" t="inlineStr">
@@ -5270,8 +6646,16 @@
 False equivalency aside, I see that you approve of the brutality of Hamas. Your antisemitic ideology is sick.</t>
         </is>
       </c>
-      <c r="E177" s="11" t="n"/>
-      <c r="F177" s="12" t="n"/>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F177" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, accuses user of justifying hamas terror</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="8" t="inlineStr">
@@ -5294,8 +6678,16 @@
           <t>Father said, bless Israel, who curse it,  I will curse them🙏</t>
         </is>
       </c>
-      <c r="E178" s="11" t="n"/>
-      <c r="F178" s="12" t="n"/>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F178" s="12" t="inlineStr">
+        <is>
+          <t>biblical blessing of israel, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="8" t="inlineStr">
@@ -5319,8 +6711,16 @@
           <t>"What the fuck did i wake up to"- me at 6:30 in the morning when running to a protected area with my family because Hamas is firing rockets at us</t>
         </is>
       </c>
-      <c r="E179" s="11" t="n"/>
-      <c r="F179" s="12" t="n"/>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F179" s="12" t="inlineStr">
+        <is>
+          <t>israeli civilian recounts fleeing hamas rockets, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="8" t="inlineStr">
@@ -5344,8 +6744,16 @@
           <t>Plenty on eye on Palestine telegram. It's not all graphic.</t>
         </is>
       </c>
-      <c r="E180" s="11" t="n"/>
-      <c r="F180" s="12" t="n"/>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F180" s="12" t="inlineStr">
+        <is>
+          <t>recommends eye on palestine channel, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="8" t="inlineStr">
@@ -5368,8 +6776,16 @@
           <t xml:space="preserve"> @crackcell  Well, it does. Get used to it.</t>
         </is>
       </c>
-      <c r="E181" s="11" t="n"/>
-      <c r="F181" s="12" t="n"/>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F181" s="12" t="inlineStr">
+        <is>
+          <t>short reply to another user, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="60" customHeight="1">
       <c r="A182" s="8" t="inlineStr">
@@ -5392,8 +6808,16 @@
           <t>The question should be what led people to believe these types of acts are acceptable. It's starts with understanding the grievences and root causes of the sentiment. A certain country's policies have led to such  conditions, where ppl have turned to an outlet that will cause destruction. Stop blaming and take responsibility and come to a resolution.</t>
         </is>
       </c>
-      <c r="E182" s="11" t="n"/>
-      <c r="F182" s="12" t="n"/>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F182" s="12" t="inlineStr">
+        <is>
+          <t>pro-palestine, points to root causes and israeli policy</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="8" t="inlineStr">
@@ -5417,8 +6841,16 @@
           <t>They can return to the Palestinian state that's the whole point of a 2 state solution</t>
         </is>
       </c>
-      <c r="E183" s="11" t="n"/>
-      <c r="F183" s="12" t="n"/>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F183" s="12" t="inlineStr">
+        <is>
+          <t>supports 2ss and refugee return to palestine, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="45" customHeight="1">
       <c r="A184" s="8" t="inlineStr">
@@ -5442,8 +6874,16 @@
           <t>No. The Arab world has untold millions of good decent people going about their lives, and their culture has given us some of the greatest scientific and cultural achievements in human history. Same goes for Palestinians.</t>
         </is>
       </c>
-      <c r="E184" s="11" t="n"/>
-      <c r="F184" s="12" t="n"/>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F184" s="12" t="inlineStr">
+        <is>
+          <t>defends palestinians and arabs against bigotry, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="8" t="inlineStr">
@@ -5466,8 +6906,16 @@
           <t>Lair</t>
         </is>
       </c>
-      <c r="E185" s="11" t="n"/>
-      <c r="F185" s="12" t="n"/>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F185" s="12" t="inlineStr">
+        <is>
+          <t>single word 'lair' (liar), stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="135" customHeight="1">
       <c r="A186" s="8" t="inlineStr">
@@ -5497,8 +6945,16 @@
 Also disclaimer, not saying all Israelis should be killed, just pointing out double standards.</t>
         </is>
       </c>
-      <c r="E186" s="11" t="n"/>
-      <c r="F186" s="12" t="n"/>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F186" s="12" t="inlineStr">
+        <is>
+          <t>calls israel apartheid/genocide, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="45" customHeight="1">
       <c r="A187" s="8" t="inlineStr">
@@ -5521,8 +6977,16 @@
           <t>Cube lah mereka biar kan Hamas di Palestin sendirian..rakyat lari ke Israel buat sementara waktu. Hamas hilang Israel akan membangun kan rumah baru untuk mereka warga Palestin..tetapi kenapa mereka dengar hasotan hamas.sampai tidak ingin lari ke Israel..</t>
         </is>
       </c>
-      <c r="E187" s="11" t="n"/>
-      <c r="F187" s="12" t="n"/>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F187" s="12" t="inlineStr">
+        <is>
+          <t>blames hamas instigation, says israel would rebuild, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="8" t="inlineStr">
@@ -5545,8 +7009,16 @@
           <t>This is why you have to educate yourself before you protests.</t>
         </is>
       </c>
-      <c r="E188" s="11" t="n"/>
-      <c r="F188" s="12" t="n"/>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F188" s="12" t="inlineStr">
+        <is>
+          <t>advises protesters to get educated, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="105" customHeight="1">
       <c r="A189" s="8" t="inlineStr">
@@ -5573,8 +7045,16 @@
 For your question though, I don't know what you should do, I am not a Eoropean nor am I American. If your choices either  calling for the destruction of Israel or do nothing than I suggest you should drop that radical mindset, honestly</t>
         </is>
       </c>
-      <c r="E189" s="11" t="n"/>
-      <c r="F189" s="12" t="n"/>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F189" s="12" t="inlineStr">
+        <is>
+          <t>rejects calls for destruction of israel, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="8" t="inlineStr">
@@ -5598,8 +7078,16 @@
           <t>It's the *l'chaim* at the end that gets me.</t>
         </is>
       </c>
-      <c r="E190" s="11" t="n"/>
-      <c r="F190" s="12" t="n"/>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F190" s="12" t="inlineStr">
+        <is>
+          <t>criticises soldiers saying l'chaim after destruction, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="8" t="inlineStr">
@@ -5622,8 +7110,16 @@
           <t>Its a freakin war. Innocent people die on both sides. ON BOTH SIDES. If ur not directly affected by the war then u shouldn't impose any of ur beliefs on anyone.</t>
         </is>
       </c>
-      <c r="E191" s="11" t="n"/>
-      <c r="F191" s="12" t="n"/>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F191" s="12" t="inlineStr">
+        <is>
+          <t>stresses innocent deaths on both sides, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="60" customHeight="1">
       <c r="A192" s="8" t="inlineStr">
@@ -5650,8 +7146,16 @@
 They were literally running for their lives.</t>
         </is>
       </c>
-      <c r="E192" s="11" t="n"/>
-      <c r="F192" s="12" t="n"/>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F192" s="12" t="inlineStr">
+        <is>
+          <t>defends jewish refugees fleeing pogroms, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="135" customHeight="1">
       <c r="A193" s="8" t="inlineStr">
@@ -5677,8 +7181,16 @@
 but at the end of the day I don't know how much it matters. people who die in wars don't "deserve" it, there is no trial system that condemns someone of guilt before shooting. in a war you shoot bc they could shoot you first. self preservation is the morality of war. And an army has an obligation to their soldiers and citizens before the enemy civilians, that's always been t</t>
         </is>
       </c>
-      <c r="E193" s="11" t="n"/>
-      <c r="F193" s="12" t="n"/>
+      <c r="E193" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>nuanced take on trauma and war, sees both sides, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="8" t="inlineStr">
@@ -5701,8 +7213,16 @@
           <t>Go allahu your fuqqbar</t>
         </is>
       </c>
-      <c r="E194" s="11" t="n"/>
-      <c r="F194" s="12" t="n"/>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F194" s="12" t="inlineStr">
+        <is>
+          <t>anti-muslim troll comment, off topic</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="8" t="inlineStr">
@@ -5725,8 +7245,16 @@
           <t xml:space="preserve"> @somirbhaitipstrick6602  or tumay dimag ki</t>
         </is>
       </c>
-      <c r="E195" s="11" t="n"/>
-      <c r="F195" s="12" t="n"/>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F195" s="12" t="inlineStr">
+        <is>
+          <t>interpersonal insult in urdu/hindi, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="8" t="inlineStr">
@@ -5749,8 +7277,16 @@
           <t>😢😢😢😢😢</t>
         </is>
       </c>
-      <c r="E196" s="11" t="n"/>
-      <c r="F196" s="12" t="n"/>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F196" s="12" t="inlineStr">
+        <is>
+          <t>crying emojis only, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="8" t="inlineStr">
@@ -5774,8 +7310,16 @@
           <t>follow</t>
         </is>
       </c>
-      <c r="E197" s="11" t="n"/>
-      <c r="F197" s="12" t="n"/>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F197" s="12" t="inlineStr">
+        <is>
+          <t>bookmarking comment, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="75" customHeight="1">
       <c r="A198" s="8" t="inlineStr">
@@ -5798,8 +7342,16 @@
           <t>Did you really think the New York Times is a paper that tells the truth?  You are clearly a biased dingbat and should probably not report or discuss the problems in Israel.  This whole region has a very complicated history that is very difficult for most people to grasp.  I would suggest that you start reading some history books.  That should keep you busy for a few years and then you might discuss the Middle East with some intelligence.</t>
         </is>
       </c>
-      <c r="E198" s="11" t="n"/>
-      <c r="F198" s="12" t="n"/>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F198" s="12" t="inlineStr">
+        <is>
+          <t>attacks video host over nyt bias, says history is complex</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="30" customHeight="1">
       <c r="A199" s="8" t="inlineStr">
@@ -5822,8 +7374,16 @@
           <t>The poor Palestinians still think they are returning to their homes... But they don't realize Israel is preparing to kick them out of the country all together.</t>
         </is>
       </c>
-      <c r="E199" s="11" t="n"/>
-      <c r="F199" s="12" t="n"/>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F199" s="12" t="inlineStr">
+        <is>
+          <t>sympathises with palestinians, accuses israel of ethnic cleansing</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="8" t="inlineStr">
@@ -5846,8 +7406,16 @@
           <t>1 Tunnel has been killed😂</t>
         </is>
       </c>
-      <c r="E200" s="11" t="n"/>
-      <c r="F200" s="12" t="n"/>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F200" s="12" t="inlineStr">
+        <is>
+          <t>mocking tunnel strike claim, unclear stance</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="30" customHeight="1">
       <c r="A201" s="8" t="inlineStr">
@@ -5871,8 +7439,16 @@
           <t>And the statement of the occupiying apartheid force is reliable?</t>
         </is>
       </c>
-      <c r="E201" s="11" t="n"/>
-      <c r="F201" s="12" t="n"/>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F201" s="12" t="inlineStr">
+        <is>
+          <t>labels idf occupying apartheid force, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="30" customHeight="1">
       <c r="A202" s="8" t="inlineStr">
@@ -5896,8 +7472,16 @@
           <t>There’s enough resources in this world to end poverty and inequality but humans are too greedy.</t>
         </is>
       </c>
-      <c r="E202" s="11" t="n"/>
-      <c r="F202" s="12" t="n"/>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F202" s="12" t="inlineStr">
+        <is>
+          <t>general philosophical comment on greed, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="135" customHeight="1">
       <c r="A203" s="8" t="inlineStr">
@@ -5923,8 +7507,16 @@
 2. **Responsibility:** Much of the ensuing suffering was not caused exclusively by Israel's siege, other contributors being A) Hamas' [abdicating responsibility for the wellbeing of the civilians to the UN and Israel](https://www.memri.org/reports/hamas-official-mousa-abu-marzouk-tunnels-gaza-were-built-protect-hamas-fighters-not) ^((hoarding of fuel and other supplies, investing in tunnels for their own protection and refusing said protection to be used by civilians, purposefully embedding themselves, and fighting from, within dense gather</t>
         </is>
       </c>
-      <c r="E203" s="11" t="n"/>
-      <c r="F203" s="12" t="n"/>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F203" s="12" t="inlineStr">
+        <is>
+          <t>pro-israel, defends gaza siege legality and blames hamas</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="30" customHeight="1">
       <c r="A204" s="8" t="inlineStr">
@@ -5948,8 +7540,16 @@
           <t>what's the diff?</t>
         </is>
       </c>
-      <c r="E204" s="11" t="n"/>
-      <c r="F204" s="12" t="n"/>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F204" s="12" t="inlineStr">
+        <is>
+          <t>vague three-word question, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="30" customHeight="1">
       <c r="A205" s="8" t="inlineStr">
@@ -5973,8 +7573,16 @@
           <t>i24 unironically loves to suck off Netanyahu’s and Trump’s D</t>
         </is>
       </c>
-      <c r="E205" s="11" t="n"/>
-      <c r="F205" s="12" t="n"/>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F205" s="12" t="inlineStr">
+        <is>
+          <t>attacks netanyahu and israeli channel i24, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="135" customHeight="1">
       <c r="A206" s="8" t="inlineStr">
@@ -6018,8 +7626,16 @@
 7. Before the Umayyad and Fatimid empires, there was the Byzantine empire, not a Palestinian state. 8. Before the Byzantine Empire, there were the Sassanids, not a Palestinian state. Al 66 9. Before the Sassanid Empire, there was the Byzantine Empire, not a Palestinian state. Palestinian state. 10. Before the Byzantine Empire, there was the Roman Empire, not a Palestinian state. 11. Before the Roman Empire, there was the Hasmonean state, not a 12. Before the Hasmonean state, there was the Seleucid, not a Palestinian state. Before the Seleucid empire, there was the empire of Alexander the Great, not a Palestinian state. 13. Before the Seleucid empire, there was the empire of Alexander the Great, not a Palestinian state. 14. Before the empire of Alexander the Great,</t>
         </is>
       </c>
-      <c r="E206" s="11" t="n"/>
-      <c r="F206" s="12" t="n"/>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F206" s="12" t="inlineStr">
+        <is>
+          <t>denies historic palestinian statehood, pro-israel argument</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="105" customHeight="1">
       <c r="A207" s="8" t="inlineStr">
@@ -6044,8 +7660,16 @@
 My personal opinion is an artist as a person is not the art they create though, so i don't exactly get not enjoying the music anymore unless it's like, a new perspective on something like... say... lyrics that make you go, huh, that's weird, but may appear worse afterwards, like many parts of harry potter. That said, i highly support not spending money on people you don't agree with or finding alternative means of enjoying their content, one of the better forms of protest in this day and age of political violence.</t>
         </is>
       </c>
-      <c r="E207" s="11" t="n"/>
-      <c r="F207" s="12" t="n"/>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F207" s="12" t="inlineStr">
+        <is>
+          <t>advocates boycotting pro-palestinian artist, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="30" customHeight="1">
       <c r="A208" s="8" t="inlineStr">
@@ -6070,8 +7694,16 @@
 The Hospital was bombed by Palestinian Islamists.</t>
         </is>
       </c>
-      <c r="E208" s="11" t="n"/>
-      <c r="F208" s="12" t="n"/>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F208" s="12" t="inlineStr">
+        <is>
+          <t>blames palestinian militants for hospital bombing, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="30" customHeight="1">
       <c r="A209" s="8" t="inlineStr">
@@ -6094,8 +7726,16 @@
           <t>❤🇮🇱🇮🇱🇮🇱🇮🇱</t>
         </is>
       </c>
-      <c r="E209" s="11" t="n"/>
-      <c r="F209" s="12" t="n"/>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F209" s="12" t="inlineStr">
+        <is>
+          <t>israel flags with heart, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="30" customHeight="1">
       <c r="A210" s="8" t="inlineStr">
@@ -6119,8 +7759,16 @@
           <t>The same people we're talking about would agree with that. People who hate Israel almost always hate America too.</t>
         </is>
       </c>
-      <c r="E210" s="11" t="n"/>
-      <c r="F210" s="12" t="n"/>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F210" s="12" t="inlineStr">
+        <is>
+          <t>links anti-israel feeling to anti-americanism, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="30" customHeight="1">
       <c r="A211" s="8" t="inlineStr">
@@ -6143,8 +7791,16 @@
           <t>I am a Christian from Indonesia, feel blessed by his teachings. Greetings from the East. Jesus bless you 💖💖</t>
         </is>
       </c>
-      <c r="E211" s="11" t="n"/>
-      <c r="F211" s="12" t="n"/>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F211" s="12" t="inlineStr">
+        <is>
+          <t>christian religious greeting, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="45" customHeight="1">
       <c r="A212" s="8" t="inlineStr">
@@ -6168,8 +7824,16 @@
           <t>Yeah Netanyahu is trying to save his Assalamualaikum from going to jail thru war. His judicial overhaul attempt is awaiting a trial and got delayed due to the war. I can’t see any reason his party is gaining anything from it. More and more protests in Tel aviv are erupting</t>
         </is>
       </c>
-      <c r="E212" s="11" t="n"/>
-      <c r="F212" s="12" t="n"/>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F212" s="12" t="inlineStr">
+        <is>
+          <t>accuses netanyahu of prolonging war to stay out of prison</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="30" customHeight="1">
       <c r="A213" s="8" t="inlineStr">
@@ -6192,8 +7856,16 @@
           <t>😂❤</t>
         </is>
       </c>
-      <c r="E213" s="11" t="n"/>
-      <c r="F213" s="12" t="n"/>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F213" s="12" t="inlineStr">
+        <is>
+          <t>laughing and heart emojis, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="30" customHeight="1">
       <c r="A214" s="8" t="inlineStr">
@@ -6217,8 +7889,16 @@
           <t>This goddamn idiot doesn't realise if he was living in West Bank he'd be spat on, harassed, assaulted and probably murdered just for the colour of his skin.</t>
         </is>
       </c>
-      <c r="E214" s="11" t="n"/>
-      <c r="F214" s="12" t="n"/>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F214" s="12" t="inlineStr">
+        <is>
+          <t>accuses west bank palestinians of violent racism, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="30" customHeight="1">
       <c r="A215" s="8" t="inlineStr">
@@ -6241,8 +7921,16 @@
           <t>The World needs Truthful people like you.  There's way too many liars.</t>
         </is>
       </c>
-      <c r="E215" s="11" t="n"/>
-      <c r="F215" s="12" t="n"/>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F215" s="12" t="inlineStr">
+        <is>
+          <t>generic compliment to creator, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="30" customHeight="1">
       <c r="A216" s="8" t="inlineStr">
@@ -6265,8 +7953,16 @@
           <t>Yo that’s kinda interesting that they really used disguises and stuff. I assume it wasn’t easy to tell</t>
         </is>
       </c>
-      <c r="E216" s="11" t="n"/>
-      <c r="F216" s="12" t="n"/>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F216" s="12" t="inlineStr">
+        <is>
+          <t>neutral remark on hospital raid disguise tactics</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="30" customHeight="1">
       <c r="A217" s="8" t="inlineStr">
@@ -6289,8 +7985,16 @@
           <t>🗺Free IsNOTreal from the world map.🗺</t>
         </is>
       </c>
-      <c r="E217" s="11" t="n"/>
-      <c r="F217" s="12" t="n"/>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F217" s="12" t="inlineStr">
+        <is>
+          <t>calls to wipe israel off map, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="135" customHeight="1">
       <c r="A218" s="8" t="inlineStr">
@@ -6318,8 +8022,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/IsraelPalestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E218" s="11" t="n"/>
-      <c r="F218" s="12" t="n"/>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F218" s="12" t="inlineStr">
+        <is>
+          <t>sub automod bot warning, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="30" customHeight="1">
       <c r="A219" s="8" t="inlineStr">
@@ -6343,8 +8055,16 @@
           <t>Most importantly, the U.S.A. is watching.</t>
         </is>
       </c>
-      <c r="E219" s="11" t="n"/>
-      <c r="F219" s="12" t="n"/>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F219" s="12" t="inlineStr">
+        <is>
+          <t>neutral observation on us attention</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="45" customHeight="1">
       <c r="A220" s="8" t="inlineStr">
@@ -6369,8 +8089,16 @@
 Also, it was never their homeland. The Jews and Christians living there are the time are also Palestinian.</t>
         </is>
       </c>
-      <c r="E220" s="11" t="n"/>
-      <c r="F220" s="12" t="n"/>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F220" s="12" t="inlineStr">
+        <is>
+          <t>questions palestinian intent toward jews, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="75" customHeight="1">
       <c r="A221" s="8" t="inlineStr">
@@ -6398,8 +8126,16 @@
 A lot of news outlets are now going back and editing their initial stories (as seen by the time they "updated") about her to say otherwise.</t>
         </is>
       </c>
-      <c r="E221" s="11" t="n"/>
-      <c r="F221" s="12" t="n"/>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F221" s="12" t="inlineStr">
+        <is>
+          <t>critiques western media misinformation on oct 7, leans p</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="45" customHeight="1">
       <c r="A222" s="8" t="inlineStr">
@@ -6423,8 +8159,16 @@
           <t>If you're a liberal you have a mental illness and you don't think straight, your post just demonstrated your compulsive judgment and dissatisfaction with people who don't think like you. Until there's a cure for your kind, this nonsense shouldn't bother anyone.</t>
         </is>
       </c>
-      <c r="E222" s="11" t="n"/>
-      <c r="F222" s="12" t="n"/>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F222" s="12" t="inlineStr">
+        <is>
+          <t>political rant against liberals, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="135" customHeight="1">
       <c r="A223" s="8" t="inlineStr">
@@ -6450,8 +8194,16 @@
 So much attention is given to how Israels actions are "radicalizing" Palestinians as if somehow the Palestinians are completely innocent for any amount of heinous activity because Israel has done so many bad things to them but don't allow the same consideration in reverse. Noone stops to think that a teenager, which is what most the Israelis troops are, that have grown up with rockets constantly flying over thier heads have not been radicalized as well. This is the problem, violence gets violence, hate gets hate. Both sides need eschew violence and hate or the natural outcome is genocide or ethnic cleansing. No people will tolerate violence against them without responding in kind and as it continues the hate will grow until it cannot be contained. The Israelis cannot do it unilaterally, the Palestinians cannot do it unilaterally, they have to become partners in peace. Until they both decide to do that at the same time the situation</t>
         </is>
       </c>
-      <c r="E223" s="11" t="n"/>
-      <c r="F223" s="12" t="n"/>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F223" s="12" t="inlineStr">
+        <is>
+          <t>blames hamas for human shields, defends idf, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="30" customHeight="1">
       <c r="A224" s="8" t="inlineStr">
@@ -6475,8 +8227,16 @@
           <t>stop the genocide and they will stop attacking the ships SIMPLE</t>
         </is>
       </c>
-      <c r="E224" s="11" t="n"/>
-      <c r="F224" s="12" t="n"/>
+      <c r="E224" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F224" s="12" t="inlineStr">
+        <is>
+          <t>defends houthi shipping attacks to stop gaza genocide</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="60" customHeight="1">
       <c r="A225" s="8" t="inlineStr">
@@ -6501,8 +8261,16 @@
 Where do people get this nonsense from? What "Jewish artifacts" would Arabs have? Palis are thoroughly Arabs and historically the most pan-Arabists of all.</t>
         </is>
       </c>
-      <c r="E225" s="11" t="n"/>
-      <c r="F225" s="12" t="n"/>
+      <c r="E225" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F225" s="12" t="inlineStr">
+        <is>
+          <t>derisive toward palestinians as 'palis', pro-israel tone</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="45" customHeight="1">
       <c r="A226" s="8" t="inlineStr">
@@ -6527,8 +8295,16 @@
 (Also this picture is very much true if you take a look at the education system in gaza, just saying)</t>
         </is>
       </c>
-      <c r="E226" s="11" t="n"/>
-      <c r="F226" s="12" t="n"/>
+      <c r="E226" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F226" s="12" t="inlineStr">
+        <is>
+          <t>defends pro-israel views and critiques gaza schools, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="30" customHeight="1">
       <c r="A227" s="8" t="inlineStr">
@@ -6551,8 +8327,16 @@
           <t>unbelivable reality</t>
         </is>
       </c>
-      <c r="E227" s="11" t="n"/>
-      <c r="F227" s="12" t="n"/>
+      <c r="E227" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F227" s="12" t="inlineStr">
+        <is>
+          <t>two-word reaction, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="8" t="inlineStr">
@@ -6576,8 +8360,16 @@
           <t>The data you presented says they are ranked fourth. Behind blacks, whites and gays.</t>
         </is>
       </c>
-      <c r="E228" s="11" t="n"/>
-      <c r="F228" s="12" t="n"/>
+      <c r="E228" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F228" s="12" t="inlineStr">
+        <is>
+          <t>factual correction on hate crime stats, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="30" customHeight="1">
       <c r="A229" s="8" t="inlineStr">
@@ -6601,8 +8393,16 @@
           <t>They are still praying, most people would have said nope. I love Palestinians, they have courage.</t>
         </is>
       </c>
-      <c r="E229" s="11" t="n"/>
-      <c r="F229" s="12" t="n"/>
+      <c r="E229" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F229" s="12" t="inlineStr">
+        <is>
+          <t>expresses love and admiration for palestinians, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="30" customHeight="1">
       <c r="A230" s="8" t="inlineStr">
@@ -6625,8 +8425,16 @@
           <t xml:space="preserve"> @julie1630  why? If u have to pay ur best friend. He is not ur friend.</t>
         </is>
       </c>
-      <c r="E230" s="11" t="n"/>
-      <c r="F230" s="12" t="n"/>
+      <c r="E230" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F230" s="12" t="inlineStr">
+        <is>
+          <t>advice on paying friends, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="30" customHeight="1">
       <c r="A231" s="8" t="inlineStr">
@@ -6650,8 +8458,16 @@
           <t>I think we all knew this. 97 percent of the “journalists” that have died in Gaza work for the propaganda wings of terrorist organizations.</t>
         </is>
       </c>
-      <c r="E231" s="11" t="n"/>
-      <c r="F231" s="12" t="n"/>
+      <c r="E231" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F231" s="12" t="inlineStr">
+        <is>
+          <t>accuses gaza journalists of working for terror orgs, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="30" customHeight="1">
       <c r="A232" s="8" t="inlineStr">
@@ -6674,8 +8490,16 @@
           <t>❤❤</t>
         </is>
       </c>
-      <c r="E232" s="11" t="n"/>
-      <c r="F232" s="12" t="n"/>
+      <c r="E232" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F232" s="12" t="inlineStr">
+        <is>
+          <t>two hearts, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="30" customHeight="1">
       <c r="A233" s="8" t="inlineStr">
@@ -6699,8 +8523,16 @@
           <t>Well there you go, you get all your news from youtube and tiktok dude</t>
         </is>
       </c>
-      <c r="E233" s="11" t="n"/>
-      <c r="F233" s="12" t="n"/>
+      <c r="E233" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F233" s="12" t="inlineStr">
+        <is>
+          <t>criticism of news sources, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="8" t="inlineStr">
@@ -6723,8 +8555,16 @@
           <t>Isnt that why the irish dont like the brits?</t>
         </is>
       </c>
-      <c r="E234" s="11" t="n"/>
-      <c r="F234" s="12" t="n"/>
+      <c r="E234" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F234" s="12" t="inlineStr">
+        <is>
+          <t>comment on irish-british relations, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="8" t="inlineStr">
@@ -6749,8 +8589,16 @@
 So stop preaching.</t>
         </is>
       </c>
-      <c r="E235" s="11" t="n"/>
-      <c r="F235" s="12" t="n"/>
+      <c r="E235" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F235" s="12" t="inlineStr">
+        <is>
+          <t>calls out selective outrage against israel, leans pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="8" t="inlineStr">
@@ -6773,8 +8621,16 @@
           <t>So she knew when to leave Britain, as it is in total chaos now😮</t>
         </is>
       </c>
-      <c r="E236" s="11" t="n"/>
-      <c r="F236" s="12" t="n"/>
+      <c r="E236" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>remark about uk being in chaos, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="75" customHeight="1">
       <c r="A237" s="8" t="inlineStr">
@@ -6799,8 +8655,16 @@
 I think it's more of a response to absolutely terrible western journalism pushing an agenda that's creating doubt in Israel, but it's certainly not benefitting Palestine at all.</t>
         </is>
       </c>
-      <c r="E237" s="11" t="n"/>
-      <c r="F237" s="12" t="n"/>
+      <c r="E237" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F237" s="12" t="inlineStr">
+        <is>
+          <t>defends israel standing and blames western media, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="45" customHeight="1">
       <c r="A238" s="8" t="inlineStr">
@@ -6826,8 +8690,16 @@
 No one should be dying in the region. The reason they are is Hamas. It’s despicable you don’t condemn their atrocities</t>
         </is>
       </c>
-      <c r="E238" s="11" t="n"/>
-      <c r="F238" s="12" t="n"/>
+      <c r="E238" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>blames hamas for all deaths, attacks user, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="8" t="inlineStr">
@@ -6851,8 +8723,16 @@
           <t>I appreciate your input @WahoosYahoo</t>
         </is>
       </c>
-      <c r="E239" s="11" t="n"/>
-      <c r="F239" s="12" t="n"/>
+      <c r="E239" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F239" s="12" t="inlineStr">
+        <is>
+          <t>acknowledging user reply, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="45" customHeight="1">
       <c r="A240" s="8" t="inlineStr">
@@ -6876,8 +8756,16 @@
           <t>Please provide me the dates when the Palestinians ruled Israel. Who was the founders and leader of palestine? I’ll wait while you go google some history and find your land never belonged to Palestinians. Crusader christians have more claim and history than Palestinians</t>
         </is>
       </c>
-      <c r="E240" s="11" t="n"/>
-      <c r="F240" s="12" t="n"/>
+      <c r="E240" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F240" s="12" t="inlineStr">
+        <is>
+          <t>denies historical palestinian claim to the land, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="8" t="inlineStr">
@@ -6900,8 +8788,16 @@
           <t xml:space="preserve"> @scottkraft1062  God bless them????</t>
         </is>
       </c>
-      <c r="E241" s="11" t="n"/>
-      <c r="F241" s="12" t="n"/>
+      <c r="E241" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F241" s="12" t="inlineStr">
+        <is>
+          <t>skeptical reaction, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="8" t="inlineStr">
@@ -6924,8 +8820,16 @@
           <t>Look, unarmed innocent civilians!</t>
         </is>
       </c>
-      <c r="E242" s="11" t="n"/>
-      <c r="F242" s="12" t="n"/>
+      <c r="E242" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F242" s="12" t="inlineStr">
+        <is>
+          <t>sarcastic pro-israel remark on gazans participating in oct 7</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="30" customHeight="1">
       <c r="A243" s="8" t="inlineStr">
@@ -6948,8 +8852,16 @@
           <t>This has got to be a fake, those two at the end had a civil conversation. Cmon man.</t>
         </is>
       </c>
-      <c r="E243" s="11" t="n"/>
-      <c r="F243" s="12" t="n"/>
+      <c r="E243" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F243" s="12" t="inlineStr">
+        <is>
+          <t>joke about civil street interview, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="30" customHeight="1">
       <c r="A244" s="8" t="inlineStr">
@@ -6972,8 +8884,16 @@
           <t>​@Ukraineballs3 the people are different then the government, remember that.</t>
         </is>
       </c>
-      <c r="E244" s="11" t="n"/>
-      <c r="F244" s="12" t="n"/>
+      <c r="E244" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F244" s="12" t="inlineStr">
+        <is>
+          <t>distinguishes civilians from governments, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="30" customHeight="1">
       <c r="A245" s="8" t="inlineStr">
@@ -6997,8 +8917,16 @@
           <t>Nah just grieve 30k people being slaughtered aimlessly</t>
         </is>
       </c>
-      <c r="E245" s="11" t="n"/>
-      <c r="F245" s="12" t="n"/>
+      <c r="E245" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F245" s="12" t="inlineStr">
+        <is>
+          <t>mourns 30k slaughtered in gaza, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="30" customHeight="1">
       <c r="A246" s="8" t="inlineStr">
@@ -7021,8 +8949,16 @@
           <t>Hurting people is bad</t>
         </is>
       </c>
-      <c r="E246" s="11" t="n"/>
-      <c r="F246" s="12" t="n"/>
+      <c r="E246" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F246" s="12" t="inlineStr">
+        <is>
+          <t>basic moral platitude against hurting people, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="30" customHeight="1">
       <c r="A247" s="8" t="inlineStr">
@@ -7045,8 +8981,16 @@
           <t>So much true</t>
         </is>
       </c>
-      <c r="E247" s="11" t="n"/>
-      <c r="F247" s="12" t="n"/>
+      <c r="E247" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F247" s="12" t="inlineStr">
+        <is>
+          <t>generic agreement, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="30" customHeight="1">
       <c r="A248" s="8" t="inlineStr">
@@ -7069,8 +9013,16 @@
           <t>Closed mind. What mind?</t>
         </is>
       </c>
-      <c r="E248" s="11" t="n"/>
-      <c r="F248" s="12" t="n"/>
+      <c r="E248" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F248" s="12" t="inlineStr">
+        <is>
+          <t>snide insult about someone's mind, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="30" customHeight="1">
       <c r="A249" s="8" t="inlineStr">
@@ -7094,8 +9046,16 @@
 каждый день такое в Газа</t>
         </is>
       </c>
-      <c r="E249" s="11" t="n"/>
-      <c r="F249" s="12" t="n"/>
+      <c r="E249" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F249" s="12" t="inlineStr">
+        <is>
+          <t>highlights constant daily hardship in gaza, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="45" customHeight="1">
       <c r="A250" s="8" t="inlineStr">
@@ -7119,8 +9079,16 @@
           <t>This is a video of an Israeli soldier showing extreme restraint while being attacked by children sent by their parents to die as “martyrs”. I can’t think of a better microcosm of this entire conflict.</t>
         </is>
       </c>
-      <c r="E250" s="11" t="n"/>
-      <c r="F250" s="12" t="n"/>
+      <c r="E250" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F250" s="12" t="inlineStr">
+        <is>
+          <t>praises idf soldier restraint, condemns palestinian parents, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="30" customHeight="1">
       <c r="A251" s="8" t="inlineStr">
@@ -7143,8 +9111,16 @@
           <t xml:space="preserve"> @ww0yrr  she is indoctrinated</t>
         </is>
       </c>
-      <c r="E251" s="11" t="n"/>
-      <c r="F251" s="12" t="n"/>
+      <c r="E251" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F251" s="12" t="inlineStr">
+        <is>
+          <t>calls speaker indoctrinated, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="30" customHeight="1">
       <c r="A252" s="8" t="inlineStr">
@@ -7168,8 +9144,16 @@
           <t>Which one of those crimes compelled Hamas leaders to stole billions from aid destined to Palestinians?</t>
         </is>
       </c>
-      <c r="E252" s="11" t="n"/>
-      <c r="F252" s="12" t="n"/>
+      <c r="E252" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F252" s="12" t="inlineStr">
+        <is>
+          <t>accuses hamas of stealing billions in aid, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="60" customHeight="1">
       <c r="A253" s="8" t="inlineStr">
@@ -7193,8 +9177,16 @@
           <t>This topic is impossible to talk honestly about. The Jews have no concept of how they anger the world and the Palestinian people have stolen women and children and are holding those Israeli citizens hostage RIGHT NOW knot 100 or 30 years ago. Right now there are Jews held in a real prison in Gaza</t>
         </is>
       </c>
-      <c r="E253" s="11" t="n"/>
-      <c r="F253" s="12" t="n"/>
+      <c r="E253" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F253" s="12" t="inlineStr">
+        <is>
+          <t>faults both sides, condemns hostages and jewish awareness, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="30" customHeight="1">
       <c r="A254" s="8" t="inlineStr">
@@ -7217,8 +9209,16 @@
           <t>​ @simonrajan3945 stop the nato supplies and see Russian flag on Ukraines admissiontrative buildings</t>
         </is>
       </c>
-      <c r="E254" s="11" t="n"/>
-      <c r="F254" s="12" t="n"/>
+      <c r="E254" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F254" s="12" t="inlineStr">
+        <is>
+          <t>about nato and ukraine-russia war, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="75" customHeight="1">
       <c r="A255" s="8" t="inlineStr">
@@ -7242,8 +9242,16 @@
           <t>That's your opinion, and i would fight for your right to have that opinion, but i haven't got to agree with you many Israeli people went by boat to the land of the Palestinian people taken there by the British and American politicians there was no god given right to that land did he negotiate the terms of the Israeli people moving there i think not so waving a religious book in the air and saying its written in law won't stand up in court 🤔</t>
         </is>
       </c>
-      <c r="E255" s="11" t="n"/>
-      <c r="F255" s="12" t="n"/>
+      <c r="E255" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F255" s="12" t="inlineStr">
+        <is>
+          <t>rejects divine entitlement to land, supports palestine</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="30" customHeight="1">
       <c r="A256" s="8" t="inlineStr">
@@ -7268,8 +9276,16 @@
 He died a loser and a deranged person who proved nothing and accomplished less.</t>
         </is>
       </c>
-      <c r="E256" s="11" t="n"/>
-      <c r="F256" s="12" t="n"/>
+      <c r="E256" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F256" s="12" t="inlineStr">
+        <is>
+          <t>disparages pro-palestine protester aaron bushnell, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="8" t="inlineStr">
@@ -7292,8 +9308,16 @@
           <t xml:space="preserve"> @elsjehansen2967 what truth???</t>
         </is>
       </c>
-      <c r="E257" s="11" t="n"/>
-      <c r="F257" s="12" t="n"/>
+      <c r="E257" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F257" s="12" t="inlineStr">
+        <is>
+          <t>short reply 'what truth', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="8" t="inlineStr">
@@ -7316,8 +9340,16 @@
           <t>He needs to talk a leaf out of king fasal book an make oil alot more expensive to america then everything will fall into place by it self he dont even have to deal with israel</t>
         </is>
       </c>
-      <c r="E258" s="11" t="n"/>
-      <c r="F258" s="12" t="n"/>
+      <c r="E258" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F258" s="12" t="inlineStr">
+        <is>
+          <t>proposes oil embargo to pressure us on israel, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="30" customHeight="1">
       <c r="A259" s="8" t="inlineStr">
@@ -7341,8 +9373,16 @@
 但 看到兩位救護人員的氛圍. 心裡有著擔心與心痛.</t>
         </is>
       </c>
-      <c r="E259" s="11" t="n"/>
-      <c r="F259" s="12" t="n"/>
+      <c r="E259" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F259" s="12" t="inlineStr">
+        <is>
+          <t>sorrow for baby and paramedics, neutral humanitarian</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="30" customHeight="1">
       <c r="A260" s="8" t="inlineStr">
@@ -7365,8 +9405,16 @@
           <t>Facts</t>
         </is>
       </c>
-      <c r="E260" s="11" t="n"/>
-      <c r="F260" s="12" t="n"/>
+      <c r="E260" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F260" s="12" t="inlineStr">
+        <is>
+          <t>single word 'facts', stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="8" t="inlineStr">
@@ -7389,8 +9437,16 @@
           <t>Well said, what Hamas did was extremely wrong and they started this war on October 7th</t>
         </is>
       </c>
-      <c r="E261" s="11" t="n"/>
-      <c r="F261" s="12" t="n"/>
+      <c r="E261" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F261" s="12" t="inlineStr">
+        <is>
+          <t>condemns hamas for oct 7 attack, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="30" customHeight="1">
       <c r="A262" s="8" t="inlineStr">
@@ -7413,8 +9469,16 @@
           <t>Meanwhile they are calling for ceasefire 😂</t>
         </is>
       </c>
-      <c r="E262" s="11" t="n"/>
-      <c r="F262" s="12" t="n"/>
+      <c r="E262" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F262" s="12" t="inlineStr">
+        <is>
+          <t>mocks ceasefire calls, pro-israel stance</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="60" customHeight="1">
       <c r="A263" s="8" t="inlineStr">
@@ -7440,8 +9504,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/IsraelPalestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E263" s="11" t="n"/>
-      <c r="F263" s="12" t="n"/>
+      <c r="E263" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F263" s="12" t="inlineStr">
+        <is>
+          <t>sub profanity bot warning, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="8" t="inlineStr">
@@ -7464,8 +9536,16 @@
           <t>Ia God, why we are so weak.</t>
         </is>
       </c>
-      <c r="E264" s="11" t="n"/>
-      <c r="F264" s="12" t="n"/>
+      <c r="E264" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F264" s="12" t="inlineStr">
+        <is>
+          <t>lamentation of weakness, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="8" t="inlineStr">
@@ -7489,8 +9569,16 @@
           <t>Less than a hundred years ago, Italians weren’t considered white in the US, things change.</t>
         </is>
       </c>
-      <c r="E265" s="11" t="n"/>
-      <c r="F265" s="12" t="n"/>
+      <c r="E265" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F265" s="12" t="inlineStr">
+        <is>
+          <t>historical note on changing definitions of race, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="135" customHeight="1">
       <c r="A266" s="8" t="inlineStr">
@@ -7517,8 +9605,16 @@
 Disrespecting Islam is where most Muslims draw the line and the last straw to be broken.</t>
         </is>
       </c>
-      <c r="E266" s="11" t="n"/>
-      <c r="F266" s="12" t="n"/>
+      <c r="E266" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>analysis of muslim public opinion on the conflict, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="30" customHeight="1">
       <c r="A267" s="8" t="inlineStr">
@@ -7541,8 +9637,16 @@
           <t>God bless and protect the IDF.</t>
         </is>
       </c>
-      <c r="E267" s="11" t="n"/>
-      <c r="F267" s="12" t="n"/>
+      <c r="E267" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F267" s="12" t="inlineStr">
+        <is>
+          <t>blessing and prayers for idf, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="60" customHeight="1">
       <c r="A268" s="8" t="inlineStr">
@@ -7567,8 +9671,16 @@
 This is true but it seems that Hamas are intent on getting justice (or whatever you want to call it) for those living in the West Bank as well, since they want the prisoners to be freed and a large volume of whom are not from Gazan.</t>
         </is>
       </c>
-      <c r="E268" s="11" t="n"/>
-      <c r="F268" s="12" t="n"/>
+      <c r="E268" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F268" s="12" t="inlineStr">
+        <is>
+          <t>analysis of hamas motives regarding prisoners, neutral</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="30" customHeight="1">
       <c r="A269" s="8" t="inlineStr">
@@ -7591,8 +9703,16 @@
           <t>i feel smthing wrong with all this bias</t>
         </is>
       </c>
-      <c r="E269" s="11" t="n"/>
-      <c r="F269" s="12" t="n"/>
+      <c r="E269" s="11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F269" s="12" t="inlineStr">
+        <is>
+          <t>criticises general media bias, stance unclear</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="45" customHeight="1">
       <c r="A270" s="8" t="inlineStr">
@@ -7616,8 +9736,16 @@
           <t>I’m an Indian Hindu. Whatever you said is derogatory and disrespectful. I will not let you and guys like you dictate whom I stand for. I’d always support Palestinians because it’s the right thing to do. Hope you heart gets freed from hatred.</t>
         </is>
       </c>
-      <c r="E270" s="11" t="n"/>
-      <c r="F270" s="12" t="n"/>
+      <c r="E270" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F270" s="12" t="inlineStr">
+        <is>
+          <t>indian hindu standing with palestinians, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="30" customHeight="1">
       <c r="A271" s="8" t="inlineStr">
@@ -7640,8 +9768,16 @@
           <t>​ @mohanforjesus gomutr 🐄💩</t>
         </is>
       </c>
-      <c r="E271" s="11" t="n"/>
-      <c r="F271" s="12" t="n"/>
+      <c r="E271" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F271" s="12" t="inlineStr">
+        <is>
+          <t>anti-hindu religious slur, irrelevant</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="45" customHeight="1">
       <c r="A272" s="8" t="inlineStr">
@@ -7665,8 +9801,16 @@
           <t>Israel is alerting civilians where to go in order to be safe. Hamas is telling them to stay for human shields or future photo opps. There’s one evil side here and that’s Hamas and anyone who supports them.</t>
         </is>
       </c>
-      <c r="E272" s="11" t="n"/>
-      <c r="F272" s="12" t="n"/>
+      <c r="E272" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F272" s="12" t="inlineStr">
+        <is>
+          <t>defends idf warnings and condemns hamas human shields, pro-israel</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="135" customHeight="1">
       <c r="A273" s="8" t="inlineStr">
@@ -7695,8 +9839,16 @@
 *I am a bot, and this action was performed automatically. Please [contact the moderators of this subreddit](/message/compose/?to=/r/Palestine) if you have any questions or concerns.*</t>
         </is>
       </c>
-      <c r="E273" s="11" t="n"/>
-      <c r="F273" s="12" t="n"/>
+      <c r="E273" s="11" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F273" s="12" t="inlineStr">
+        <is>
+          <t>palestine sub automod rules, pro-palestine</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="30" customHeight="1">
       <c r="A274" s="8" t="inlineStr">
@@ -7720,8 +9872,16 @@
           <t>If you want to know about a comprehensive history surrounding Atatürk get the one from Andrew Mango. Nutuk or the great speech is a bit too specific.</t>
         </is>
       </c>
-      <c r="E274" s="11" t="n"/>
-      <c r="F274" s="12" t="n"/>
+      <c r="E274" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F274" s="12" t="inlineStr">
+        <is>
+          <t>book recommendation on ataturk, irrelevant</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:F274"/>
